--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_90_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_90_R9.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2749</v>
+        <v>6.087</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8177</v>
+        <v>4.0667</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4572</v>
+        <v>2.0203</v>
       </c>
       <c r="G2" t="n">
         <v>1.5333</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6178</v>
+        <v>1.4299</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1429</v>
+        <v>1.3919</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4749</v>
+        <v>0.038</v>
       </c>
       <c r="V2" t="n">
         <v>2.428</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1604</v>
+        <v>4.4717</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7829</v>
+        <v>3.3293</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3776</v>
+        <v>1.1423</v>
       </c>
       <c r="G3" t="n">
         <v>2.2742</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1138</v>
+        <v>0.1975</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1924</v>
+        <v>0.3541</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0786</v>
+        <v>-0.1566</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9977</v>
+        <v>2.3469</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9785</v>
+        <v>1.9916</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0191</v>
+        <v>0.3552</v>
       </c>
       <c r="G4" t="n">
         <v>0.7212</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5806</v>
+        <v>0.9298</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0093</v>
+        <v>1.0225</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4288</v>
+        <v>-0.0927</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6984</v>
+        <v>1.6797</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1729</v>
+        <v>2.5118</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8713</v>
+        <v>-0.8321</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7408</v>
+        <v>3.5801</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4503</v>
+        <v>3.1955</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7095</v>
+        <v>0.3846</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6796</v>
+        <v>3.2517</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9741</v>
+        <v>2.8638</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2944</v>
+        <v>0.3879</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0612</v>
+        <v>0.3284</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4762</v>
+        <v>0.3317</v>
       </c>
       <c r="O5" t="n">
-        <v>0.415</v>
+        <v>-0.0033</v>
       </c>
       <c r="P5" t="n">
         <v>-1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7834</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8489</v>
+        <v>0.0068</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0761</v>
+        <v>0.7393</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7727000000000001</v>
+        <v>-0.7325</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>-0.2836</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1339</v>
+        <v>1.0723</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2012</v>
+        <v>1.3274</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0673</v>
+        <v>-0.2552</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5801</v>
+        <v>0.6944</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1955</v>
+        <v>1.8019</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3846</v>
+        <v>-1.1075</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2517</v>
+        <v>1.4059</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8638</v>
+        <v>1.6168</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3879</v>
+        <v>-0.2109</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3284</v>
+        <v>-0.7115</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3317</v>
+        <v>0.1852</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0033</v>
+        <v>-0.8966</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.539</v>
+        <v>-0.0138</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4288</v>
+        <v>0.1535</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9678</v>
+        <v>-0.1674</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3558</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5765</v>
+        <v>0.8139</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8989</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3224</v>
+        <v>-0.1755</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6944</v>
+        <v>1.4851</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8019</v>
+        <v>-2.3191</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1075</v>
+        <v>3.8042</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4059</v>
+        <v>3.2261</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6168</v>
+        <v>-1.371</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2109</v>
+        <v>4.5971</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7115</v>
+        <v>-1.7409</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1852</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8966</v>
+        <v>-0.7929</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.2566</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.275</v>
+        <v>0.3148</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2346</v>
+        <v>-0.0582</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RUBSTAVICIUS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1377</v>
+        <v>0.2656</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1494</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0116</v>
+        <v>1.2328</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1465</v>
+        <v>-0.7408</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1465</v>
+        <v>-1.4503</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.7095</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.6796</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.9741</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.2944</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1465</v>
+        <v>-0.0612</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1465</v>
+        <v>-0.4762</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.7834</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2842</v>
+        <v>1.4161</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>1.2819</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1349</v>
+        <v>0.1342</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>M. RUBSTAVICIUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2874</v>
+        <v>-0.1041</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3249</v>
+        <v>-0.1494</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.0452</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4851</v>
+        <v>0.1465</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3191</v>
+        <v>0.1465</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8042</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2261</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.371</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4.5971</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7409</v>
+        <v>0.1465</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9481000000000001</v>
+        <v>0.1465</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7929</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8448</v>
+        <v>-0.2506</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3497</v>
+        <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4951</v>
+        <v>-0.1013</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7583</v>
+        <v>-1.7406</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5745</v>
+        <v>-1.7921</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1838</v>
+        <v>0.0515</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8147</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6963</v>
+        <v>0.3213</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2003</v>
+        <v>0.5821</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.496</v>
+        <v>-0.2607</v>
       </c>
       <c r="V10" t="n">
         <v>1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6144</v>
+        <v>-3.2366</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7833</v>
+        <v>-3.4727</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1689</v>
+        <v>0.2361</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7957</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2689</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.8887</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3093</v>
+        <v>-0.242</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9975</v>
+        <v>-3.8624</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8572</v>
+        <v>-1.6213</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1403</v>
+        <v>-2.2411</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6726</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1419</v>
+        <v>-0.0068</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2082</v>
+        <v>0.0277</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0663</v>
+        <v>-0.0345</v>
       </c>
       <c r="V12" t="n">
         <v>-1.719</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.046499999999998</v>
+        <v>7.793399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4668</v>
+        <v>6.2135</v>
       </c>
       <c r="F13" t="n">
-        <v>1.579499999999999</v>
+        <v>1.5795</v>
       </c>
       <c r="G13" t="n">
-        <v>5.411</v>
+        <v>5.410999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4089999999999999</v>
+        <v>0.4089999999999995</v>
       </c>
       <c r="I13" t="n">
-        <v>5.001999999999999</v>
+        <v>5.002</v>
       </c>
       <c r="J13" t="n">
-        <v>9.631500000000001</v>
+        <v>9.631499999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0.9163000000000001</v>
@@ -1453,10 +1453,10 @@
         <v>-4.220599999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5072000000000003</v>
+        <v>-0.5072000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.713200000000001</v>
+        <v>-3.7132</v>
       </c>
       <c r="P13" t="n">
         <v>-5.7988</v>
@@ -1468,13 +1468,13 @@
         <v>10.4381</v>
       </c>
       <c r="S13" t="n">
-        <v>4.186600000000001</v>
+        <v>4.9335</v>
       </c>
       <c r="T13" t="n">
-        <v>5.8602</v>
+        <v>6.6071</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.674</v>
+        <v>-1.6737</v>
       </c>
       <c r="V13" t="n">
         <v>3.247699999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.085</v>
+        <v>3.7643</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7626</v>
+        <v>3.5883</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6776</v>
+        <v>0.176</v>
       </c>
       <c r="G14" t="n">
         <v>1.7415</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.744</v>
+        <v>-0.0648</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.955</v>
+        <v>-0.1294</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.789</v>
+        <v>0.0646</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9352</v>
+        <v>1.4184</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1783</v>
+        <v>0.0576</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1135</v>
+        <v>1.3608</v>
       </c>
       <c r="G15" t="n">
         <v>0.2151</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.4147</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1415</v>
+        <v>0.0944</v>
       </c>
       <c r="U15" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.3203</v>
       </c>
       <c r="V15" t="n">
         <v>0.7886</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3676</v>
+        <v>0.615</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6834</v>
+        <v>0.2116</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3158</v>
+        <v>0.4034</v>
       </c>
       <c r="G16" t="n">
         <v>0.4278</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1871</v>
+        <v>0.4345</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9831</v>
+        <v>0.5113</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.796</v>
+        <v>-0.0769</v>
       </c>
       <c r="V16" t="n">
         <v>1.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0359</v>
+        <v>-0.0824</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7703</v>
+        <v>0.1453</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.2277</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5531</v>
+        <v>0.2826</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0502</v>
+        <v>-0.5774</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.6032</v>
+        <v>0.86</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3271</v>
+        <v>0.4754</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6405</v>
+        <v>-0.7023</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9676</v>
+        <v>1.1778</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.226</v>
+        <v>-0.1929</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5904</v>
+        <v>0.1249</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.3178</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>1.357</v>
+        <v>-0.919</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2571</v>
+        <v>-0.3301</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9001</v>
+        <v>-0.5889</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0349</v>
+        <v>-0.2125</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0274</v>
+        <v>-0.1536</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0076</v>
+        <v>-0.0589</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2826</v>
+        <v>-0.5084</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5774</v>
+        <v>0.1909</v>
       </c>
       <c r="I18" t="n">
-        <v>0.86</v>
+        <v>-0.6993</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4754</v>
+        <v>0.0704</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7023</v>
+        <v>0.0336</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1778</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1929</v>
+        <v>-0.5788</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1249</v>
+        <v>0.1573</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3178</v>
+        <v>-0.7361</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8017</v>
+        <v>-0.168</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4481</v>
+        <v>-0.224</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3536</v>
+        <v>0.056</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2462</v>
+        <v>-0.2825</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1536</v>
+        <v>-0.8159</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0925</v>
+        <v>0.5335</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5084</v>
+        <v>-0.8973</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1909</v>
+        <v>1.281</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6993</v>
+        <v>-2.1783</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0704</v>
+        <v>0.1391</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0336</v>
+        <v>1.21</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-1.0709</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5788</v>
+        <v>-1.0364</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7361</v>
+        <v>-1.1074</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2016</v>
+        <v>0.2025</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>0.2047</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0224</v>
+        <v>-0.0022</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.361</v>
+        <v>-0.504</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2726</v>
+        <v>-2.0406</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6336</v>
+        <v>1.5367</v>
       </c>
       <c r="G20" t="n">
-        <v>0.73</v>
+        <v>-0.7347</v>
       </c>
       <c r="H20" t="n">
-        <v>1.359</v>
+        <v>-1.5981</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.629</v>
+        <v>0.8633</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2195</v>
+        <v>-0.7278</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1091</v>
+        <v>-2.016</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1104</v>
+        <v>1.2882</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4895</v>
+        <v>-0.0069</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2499</v>
+        <v>0.4179</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.4248</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4503</v>
+        <v>-0.3233</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8417</v>
+        <v>-0.1531</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3914</v>
+        <v>-0.1702</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.933</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3726</v>
+        <v>-0.529</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8159</v>
+        <v>0.8008</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4434</v>
+        <v>-1.3298</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8973</v>
+        <v>0.73</v>
       </c>
       <c r="H21" t="n">
-        <v>1.281</v>
+        <v>1.359</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1783</v>
+        <v>-0.629</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1391</v>
+        <v>1.2195</v>
       </c>
       <c r="K21" t="n">
-        <v>1.21</v>
+        <v>1.1091</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0709</v>
+        <v>0.1104</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0364</v>
+        <v>-0.4895</v>
       </c>
       <c r="N21" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.2499</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1074</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1125</v>
+        <v>0.2822</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2047</v>
+        <v>0.3699</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0922</v>
+        <v>-0.0876</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2836</v>
+        <v>-2.933</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2836</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2432</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1292</v>
+        <v>-0.6451</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1141</v>
+        <v>-0.0045</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9384</v>
+        <v>-1.5531</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6678</v>
+        <v>1.0502</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7294</v>
+        <v>-2.6032</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1914</v>
+        <v>-0.3271</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7521</v>
+        <v>1.6405</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9435</v>
+        <v>-1.9676</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1298</v>
+        <v>-1.226</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9157</v>
+        <v>-0.5904</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.214</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.391</v>
+        <v>0.6715</v>
       </c>
       <c r="T22" t="n">
-        <v>0.999</v>
+        <v>0.8417</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.608</v>
+        <v>-0.1702</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.542</v>
+        <v>-1.3726</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3945</v>
+        <v>-1.483</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8525</v>
+        <v>0.1104</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7347</v>
+        <v>-0.9384</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5981</v>
+        <v>-1.6678</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8633</v>
+        <v>0.7294</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7278</v>
+        <v>0.1914</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.016</v>
+        <v>-0.7521</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2882</v>
+        <v>0.9435</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0069</v>
+        <v>-1.1298</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4179</v>
+        <v>-0.9157</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4248</v>
+        <v>-0.214</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3614</v>
+        <v>0.2616</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.507</v>
+        <v>0.6451</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8544</v>
+        <v>-0.3835</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.67</v>
+        <v>-2.0638</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0385</v>
+        <v>-0.5667</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6315</v>
+        <v>-1.4971</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6206</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1369</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4402</v>
+        <v>0.0316</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6967</v>
+        <v>-0.5623</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.07</v>
+        <v>-3.2158</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.458</v>
+        <v>-1.7503</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6121</v>
+        <v>-1.4656</v>
       </c>
       <c r="G25" t="n">
         <v>-2.5555</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3702</v>
+        <v>-0.516</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8962</v>
+        <v>-0.1885</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.474</v>
+        <v>-0.3275</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.0464</v>
+        <v>-3.1146</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6517</v>
+        <v>-2.6516</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.3946</v>
+        <v>-0.4628000000000008</v>
       </c>
       <c r="G26" t="n">
         <v>-5.411</v>
@@ -2455,19 +2455,19 @@
         <v>-5.0021</v>
       </c>
       <c r="J26" t="n">
-        <v>4.220299999999999</v>
+        <v>4.2203</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5071999999999997</v>
+        <v>0.5072000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>3.7132</v>
+        <v>3.713199999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.631399999999999</v>
+        <v>-9.631400000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.9164000000000001</v>
+        <v>-0.9164000000000003</v>
       </c>
       <c r="O26" t="n">
         <v>-8.715100000000001</v>
@@ -2482,13 +2482,13 @@
         <v>16.2368</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.1864</v>
+        <v>-0.2547999999999999</v>
       </c>
       <c r="T26" t="n">
         <v>1.6736</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.8601</v>
+        <v>-1.9284</v>
       </c>
       <c r="V26" t="n">
         <v>-3.2477</v>
